--- a/Design-Files/Project Outputs for Phone_Charger/Phone_Charger.xlsx
+++ b/Design-Files/Project Outputs for Phone_Charger/Phone_Charger.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Phone_Charger!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="229">
   <si>
     <t>Comment</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Quantity</t>
   </si>
   <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>CC0603ZRY5V9BB104</t>
   </si>
   <si>
+    <t>Yageo</t>
+  </si>
+  <si>
     <t>22uF</t>
   </si>
   <si>
@@ -89,6 +95,9 @@
     <t>UWX1H100MCL1GB</t>
   </si>
   <si>
+    <t>Nichicon</t>
+  </si>
+  <si>
     <t>100pF</t>
   </si>
   <si>
@@ -128,6 +137,9 @@
     <t>C0402C222J3GEC7867</t>
   </si>
   <si>
+    <t>KEMET</t>
+  </si>
+  <si>
     <t>CAP CER 10UF 25V X5R 0603</t>
   </si>
   <si>
@@ -149,6 +161,9 @@
     <t>0603ZC102KAT2A</t>
   </si>
   <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
     <t>SS34</t>
   </si>
   <si>
@@ -161,6 +176,9 @@
     <t>SMA</t>
   </si>
   <si>
+    <t>Changzhou</t>
+  </si>
+  <si>
     <t>LESD5Z5.0CT1G</t>
   </si>
   <si>
@@ -170,6 +188,9 @@
     <t>D2</t>
   </si>
   <si>
+    <t>UMW</t>
+  </si>
+  <si>
     <t>SDM2U20SD3-7</t>
   </si>
   <si>
@@ -179,6 +200,9 @@
     <t>D3, D4</t>
   </si>
   <si>
+    <t>Diodes</t>
+  </si>
+  <si>
     <t>DC-C024E-7A-1.65</t>
   </si>
   <si>
@@ -188,6 +212,9 @@
     <t>J1</t>
   </si>
   <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
     <t>901-141A1011D10100</t>
   </si>
   <si>
@@ -197,6 +224,9 @@
     <t>J2, J3</t>
   </si>
   <si>
+    <t>Jing Extension of the Electronic Co.</t>
+  </si>
+  <si>
     <t>U241-041N-1BR85-1</t>
   </si>
   <si>
@@ -221,6 +251,9 @@
     <t>MGFL2012F100MT-LF</t>
   </si>
   <si>
+    <t>Microgate</t>
+  </si>
+  <si>
     <t>4.7uH</t>
   </si>
   <si>
@@ -233,6 +266,9 @@
     <t>NR5040T4R7N</t>
   </si>
   <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
     <t>1uH</t>
   </si>
   <si>
@@ -257,6 +293,9 @@
     <t>LED 0402</t>
   </si>
   <si>
+    <t>TUOZHAN</t>
+  </si>
+  <si>
     <t>2835 SMD LED</t>
   </si>
   <si>
@@ -269,6 +308,9 @@
     <t>2835 LED</t>
   </si>
   <si>
+    <t>ENLINCA</t>
+  </si>
+  <si>
     <t>61300611121</t>
   </si>
   <si>
@@ -281,6 +323,9 @@
     <t>HDR1X6</t>
   </si>
   <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
     <t>826629-2</t>
   </si>
   <si>
@@ -293,6 +338,9 @@
     <t>HDR1X2</t>
   </si>
   <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
     <t>SI2302-TP</t>
   </si>
   <si>
@@ -302,6 +350,9 @@
     <t>Q1</t>
   </si>
   <si>
+    <t>MCC</t>
+  </si>
+  <si>
     <t>DMN1045UFR4-7</t>
   </si>
   <si>
@@ -323,6 +374,9 @@
     <t>SOT-23-6</t>
   </si>
   <si>
+    <t>TECH</t>
+  </si>
+  <si>
     <t>1K</t>
   </si>
   <si>
@@ -362,6 +416,9 @@
     <t>WSL0603R0500FEA</t>
   </si>
   <si>
+    <t>Vishay Dale</t>
+  </si>
+  <si>
     <t>0R</t>
   </si>
   <si>
@@ -380,7 +437,7 @@
     <t>RES SMD 10K OHM 5% 1/10W 0603</t>
   </si>
   <si>
-    <t>R6, R10, R15, R16, R19, R23, R?</t>
+    <t>R6, R10, R15, R16, R17, R19, R23</t>
   </si>
   <si>
     <t>AC0603JR-0710KL</t>
@@ -401,6 +458,9 @@
     <t>PA2512JKF7W0R001E</t>
   </si>
   <si>
+    <t>YEGEO</t>
+  </si>
+  <si>
     <t>12K</t>
   </si>
   <si>
@@ -413,6 +473,9 @@
     <t>ERJ3EKF1202V</t>
   </si>
   <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
     <t>33K</t>
   </si>
   <si>
@@ -437,6 +500,9 @@
     <t>RC0603FR-073K3L</t>
   </si>
   <si>
+    <t>Yageo Phycomp</t>
+  </si>
+  <si>
     <t>470K</t>
   </si>
   <si>
@@ -473,6 +539,9 @@
     <t>ERJU3RD3300V</t>
   </si>
   <si>
+    <t>PANASONIC</t>
+  </si>
+  <si>
     <t>732K</t>
   </si>
   <si>
@@ -509,6 +578,9 @@
     <t>SW1</t>
   </si>
   <si>
+    <t>XKB</t>
+  </si>
+  <si>
     <t>SKHHLQA010</t>
   </si>
   <si>
@@ -518,6 +590,9 @@
     <t>SW2</t>
   </si>
   <si>
+    <t>ALPSALPINE</t>
+  </si>
+  <si>
     <t>ATMEGA328P-AU</t>
   </si>
   <si>
@@ -530,6 +605,9 @@
     <t>32 TQFP (7X7)</t>
   </si>
   <si>
+    <t>Microchip / Atmel</t>
+  </si>
+  <si>
     <t>TP5000_QFN16</t>
   </si>
   <si>
@@ -542,6 +620,9 @@
     <t>16-QFN (4x4)</t>
   </si>
   <si>
+    <t>TOPPOWER</t>
+  </si>
+  <si>
     <t>BD48K29G-TL</t>
   </si>
   <si>
@@ -554,6 +635,9 @@
     <t>3-SSOP</t>
   </si>
   <si>
+    <t>Rohm</t>
+  </si>
+  <si>
     <t>SLG7NT402V</t>
   </si>
   <si>
@@ -563,6 +647,9 @@
     <t>U4</t>
   </si>
   <si>
+    <t>Dialog Semiconductor</t>
+  </si>
+  <si>
     <t>NC7SZ05P5X</t>
   </si>
   <si>
@@ -572,6 +659,9 @@
     <t>U5</t>
   </si>
   <si>
+    <t>ON Semiconductor / Fairchild</t>
+  </si>
+  <si>
     <t>INA181A3IDBVR</t>
   </si>
   <si>
@@ -581,6 +671,9 @@
     <t>U6</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>TPS2115ADRBTG4</t>
   </si>
   <si>
@@ -608,6 +701,9 @@
     <t>U9</t>
   </si>
   <si>
+    <t>onsemi</t>
+  </si>
+  <si>
     <t>Q24FA20H0051200</t>
   </si>
   <si>
@@ -615,6 +711,9 @@
   </si>
   <si>
     <t>X1</t>
+  </si>
+  <si>
+    <t>Seiko Epson</t>
   </si>
 </sst>
 </file>
@@ -630,7 +729,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,6 +739,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -671,7 +776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -681,6 +786,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -966,13 +1074,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -991,1010 +1100,1157 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="F2" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F3" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="F4" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="F5" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>27</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="F7" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
+      <c r="G7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
+      <c r="G8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>40</v>
+      <c r="G9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
+      <c r="G10" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>47</v>
+      <c r="G11" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>50</v>
+      <c r="G12" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>53</v>
+      <c r="G13" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>56</v>
+      <c r="G14" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>63</v>
+    </row>
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>67</v>
+      <c r="G16" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="F17" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>71</v>
+      <c r="G17" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>72</v>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="F19" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>76</v>
+      <c r="G19" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="F20" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>80</v>
+      <c r="G20" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="F21" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>84</v>
+      <c r="G21" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>88</v>
+      <c r="G22" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F23" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>91</v>
+      <c r="G23" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="F24" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>94</v>
+      <c r="G24" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="F25" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>102</v>
+      <c r="G25" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="F26" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>106</v>
+      <c r="G26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="F27" s="4">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>110</v>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="F28" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>114</v>
+      <c r="G28" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="F29" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>118</v>
+      <c r="G29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="F30" s="4">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>127</v>
+      <c r="E32" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>131</v>
+      <c r="G32" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="F33" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>135</v>
+      <c r="G33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="F34" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>139</v>
+      <c r="G34" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="F35" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>143</v>
+      <c r="G35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="F36" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>147</v>
+      <c r="G36" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="F37" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>151</v>
+      <c r="G37" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="F38" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>156</v>
+      <c r="G38" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="F39" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>157</v>
+      <c r="G39" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>160</v>
+      <c r="G40" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="F41" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>163</v>
+      <c r="G41" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>188</v>
       </c>
       <c r="F42" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>167</v>
+      <c r="G42" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="F43" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>171</v>
+      <c r="G43" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>198</v>
       </c>
       <c r="F44" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>175</v>
+      <c r="G44" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="F45" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>178</v>
+      <c r="G45" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="F46" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>181</v>
+      <c r="G46" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="F47" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>184</v>
+      <c r="G47" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="F48" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>187</v>
+      <c r="G48" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="F49" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>190</v>
+      <c r="G49" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="F50" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>193</v>
+      <c r="G50" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="F51" s="4">
         <v>1</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="28" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageSetup scale="27" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
 </worksheet>
 </file>